--- a/analysis/llm_explanations/annotations/input/LLM Uitleg Evaluatie — Alcoholwetvergunning — Juristen (Responses).xlsx
+++ b/analysis/llm_explanations/annotations/input/LLM Uitleg Evaluatie — Alcoholwetvergunning — Juristen (Responses).xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\floor\Documents\GitHub\poc-machine-law\analysis\llm_explanations\annotations\input\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFD494C-00EA-4110-8144-A97BF21969CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Form responses 1" sheetId="1" r:id="rId5"/>
+    <sheet name="Form responses 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="144">
   <si>
     <t>Timestamp</t>
   </si>
@@ -22,9 +31,6 @@
     <t>Specialisatie (optioneel)</t>
   </si>
   <si>
-    <t>Wil je kans maken op €50? Laat dan je e-mailadres achter.</t>
-  </si>
-  <si>
     <t>1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct)</t>
   </si>
   <si>
@@ -331,9 +337,6 @@
     <t>fiscaal</t>
   </si>
   <si>
-    <t>ednic@live.nl</t>
-  </si>
-  <si>
     <t>mi akkoord</t>
   </si>
   <si>
@@ -391,13 +394,7 @@
     <t>snackbar geen alcohol</t>
   </si>
   <si>
-    <t>0-2 jaar</t>
-  </si>
-  <si>
     <t>Strafrecht</t>
-  </si>
-  <si>
-    <t>meryem-antek@hotmail.com</t>
   </si>
   <si>
     <t>Dit is niet geheel gebaseerd op art. 3 Alcoholwet</t>
@@ -453,23 +450,27 @@
   </si>
   <si>
     <t>Andere factoren van afwijzingen dienen er ook in te staan</t>
+  </si>
+  <si>
+    <t>leeftijd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -480,79 +481,46 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <border>
         <left style="thin">
@@ -569,140 +537,163 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B3F86"/>
+          <bgColor rgb="FF5B3F86"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Form responses 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Form responses 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:CZ3" displayName="Form_Responses" name="Form_Responses" id="1">
-  <tableColumns count="104">
-    <tableColumn name="Timestamp" id="1"/>
-    <tableColumn name="Jaren juridische ervaring" id="2"/>
-    <tableColumn name="Specialisatie (optioneel)" id="3"/>
-    <tableColumn name="Wil je kans maken op €50? Laat dan je e-mailadres achter." id="4"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct)" id="5"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel)" id="6"/>
-    <tableColumn name="2. Mist er relevante juridische informatie?" id="7"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel)" id="8"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht?" id="9"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 2" id="10"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 2" id="11"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 2" id="12"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 2" id="13"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 2" id="14"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 3" id="15"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 3" id="16"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 3" id="17"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 3" id="18"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 3" id="19"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 4" id="20"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 4" id="21"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 4" id="22"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 4" id="23"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 4" id="24"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 5" id="25"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 5" id="26"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 5" id="27"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 5" id="28"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 5" id="29"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 6" id="30"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 6" id="31"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 6" id="32"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 6" id="33"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 6" id="34"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 7" id="35"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 7" id="36"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 7" id="37"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 7" id="38"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 7" id="39"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 8" id="40"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 8" id="41"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 8" id="42"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 8" id="43"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 8" id="44"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 9" id="45"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 9" id="46"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 9" id="47"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 9" id="48"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 9" id="49"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 10" id="50"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 10" id="51"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 10" id="52"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 10" id="53"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 10" id="54"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 11" id="55"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 11" id="56"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 11" id="57"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 11" id="58"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 11" id="59"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 12" id="60"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 12" id="61"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 12" id="62"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 12" id="63"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 12" id="64"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 13" id="65"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 13" id="66"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 13" id="67"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 13" id="68"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 13" id="69"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 14" id="70"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 14" id="71"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 14" id="72"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 14" id="73"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 14" id="74"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 15" id="75"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 15" id="76"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 15" id="77"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 15" id="78"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 15" id="79"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 16" id="80"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 16" id="81"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 16" id="82"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 16" id="83"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 16" id="84"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 17" id="85"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 17" id="86"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 17" id="87"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 17" id="88"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 17" id="89"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 18" id="90"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 18" id="91"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 18" id="92"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 18" id="93"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 18" id="94"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 19" id="95"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 19" id="96"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 19" id="97"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 19" id="98"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 19" id="99"/>
-    <tableColumn name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 20" id="100"/>
-    <tableColumn name="Toelichting bij vraag 1 (optioneel) 20" id="101"/>
-    <tableColumn name="2. Mist er relevante juridische informatie? 20" id="102"/>
-    <tableColumn name="Toelichting bij vraag 2 (optioneel) 20" id="103"/>
-    <tableColumn name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 20" id="104"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:CY4">
+  <tableColumns count="103">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Timestamp"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Jaren juridische ervaring"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Specialisatie (optioneel)"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct)"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Toelichting bij vraag 1 (optioneel)"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="2. Mist er relevante juridische informatie?"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Toelichting bij vraag 2 (optioneel)"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht?"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 2"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Toelichting bij vraag 1 (optioneel) 2"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="2. Mist er relevante juridische informatie? 2"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Toelichting bij vraag 2 (optioneel) 2"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 2"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 3"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Toelichting bij vraag 1 (optioneel) 3"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="2. Mist er relevante juridische informatie? 3"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Toelichting bij vraag 2 (optioneel) 3"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 3"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 4"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Toelichting bij vraag 1 (optioneel) 4"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="2. Mist er relevante juridische informatie? 4"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Toelichting bij vraag 2 (optioneel) 4"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 4"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 5"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Toelichting bij vraag 1 (optioneel) 5"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="2. Mist er relevante juridische informatie? 5"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Toelichting bij vraag 2 (optioneel) 5"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 5"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 6"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Toelichting bij vraag 1 (optioneel) 6"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="2. Mist er relevante juridische informatie? 6"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Toelichting bij vraag 2 (optioneel) 6"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 6"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 7"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Toelichting bij vraag 1 (optioneel) 7"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="2. Mist er relevante juridische informatie? 7"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Toelichting bij vraag 2 (optioneel) 7"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 7"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 8"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Toelichting bij vraag 1 (optioneel) 8"/>
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="2. Mist er relevante juridische informatie? 8"/>
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="Toelichting bij vraag 2 (optioneel) 8"/>
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 8"/>
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 9"/>
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="Toelichting bij vraag 1 (optioneel) 9"/>
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="2. Mist er relevante juridische informatie? 9"/>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="Toelichting bij vraag 2 (optioneel) 9"/>
+    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 9"/>
+    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 10"/>
+    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Toelichting bij vraag 1 (optioneel) 10"/>
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="2. Mist er relevante juridische informatie? 10"/>
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="Toelichting bij vraag 2 (optioneel) 10"/>
+    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 10"/>
+    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 11"/>
+    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Toelichting bij vraag 1 (optioneel) 11"/>
+    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="2. Mist er relevante juridische informatie? 11"/>
+    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Toelichting bij vraag 2 (optioneel) 11"/>
+    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 11"/>
+    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 12"/>
+    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Toelichting bij vraag 1 (optioneel) 12"/>
+    <tableColumn id="62" xr3:uid="{00000000-0010-0000-0000-00003E000000}" name="2. Mist er relevante juridische informatie? 12"/>
+    <tableColumn id="63" xr3:uid="{00000000-0010-0000-0000-00003F000000}" name="Toelichting bij vraag 2 (optioneel) 12"/>
+    <tableColumn id="64" xr3:uid="{00000000-0010-0000-0000-000040000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 12"/>
+    <tableColumn id="65" xr3:uid="{00000000-0010-0000-0000-000041000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 13"/>
+    <tableColumn id="66" xr3:uid="{00000000-0010-0000-0000-000042000000}" name="Toelichting bij vraag 1 (optioneel) 13"/>
+    <tableColumn id="67" xr3:uid="{00000000-0010-0000-0000-000043000000}" name="2. Mist er relevante juridische informatie? 13"/>
+    <tableColumn id="68" xr3:uid="{00000000-0010-0000-0000-000044000000}" name="Toelichting bij vraag 2 (optioneel) 13"/>
+    <tableColumn id="69" xr3:uid="{00000000-0010-0000-0000-000045000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 13"/>
+    <tableColumn id="70" xr3:uid="{00000000-0010-0000-0000-000046000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 14"/>
+    <tableColumn id="71" xr3:uid="{00000000-0010-0000-0000-000047000000}" name="Toelichting bij vraag 1 (optioneel) 14"/>
+    <tableColumn id="72" xr3:uid="{00000000-0010-0000-0000-000048000000}" name="2. Mist er relevante juridische informatie? 14"/>
+    <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Toelichting bij vraag 2 (optioneel) 14"/>
+    <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 14"/>
+    <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 15"/>
+    <tableColumn id="76" xr3:uid="{00000000-0010-0000-0000-00004C000000}" name="Toelichting bij vraag 1 (optioneel) 15"/>
+    <tableColumn id="77" xr3:uid="{00000000-0010-0000-0000-00004D000000}" name="2. Mist er relevante juridische informatie? 15"/>
+    <tableColumn id="78" xr3:uid="{00000000-0010-0000-0000-00004E000000}" name="Toelichting bij vraag 2 (optioneel) 15"/>
+    <tableColumn id="79" xr3:uid="{00000000-0010-0000-0000-00004F000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 15"/>
+    <tableColumn id="80" xr3:uid="{00000000-0010-0000-0000-000050000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 16"/>
+    <tableColumn id="81" xr3:uid="{00000000-0010-0000-0000-000051000000}" name="Toelichting bij vraag 1 (optioneel) 16"/>
+    <tableColumn id="82" xr3:uid="{00000000-0010-0000-0000-000052000000}" name="2. Mist er relevante juridische informatie? 16"/>
+    <tableColumn id="83" xr3:uid="{00000000-0010-0000-0000-000053000000}" name="Toelichting bij vraag 2 (optioneel) 16"/>
+    <tableColumn id="84" xr3:uid="{00000000-0010-0000-0000-000054000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 16"/>
+    <tableColumn id="85" xr3:uid="{00000000-0010-0000-0000-000055000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 17"/>
+    <tableColumn id="86" xr3:uid="{00000000-0010-0000-0000-000056000000}" name="Toelichting bij vraag 1 (optioneel) 17"/>
+    <tableColumn id="87" xr3:uid="{00000000-0010-0000-0000-000057000000}" name="2. Mist er relevante juridische informatie? 17"/>
+    <tableColumn id="88" xr3:uid="{00000000-0010-0000-0000-000058000000}" name="Toelichting bij vraag 2 (optioneel) 17"/>
+    <tableColumn id="89" xr3:uid="{00000000-0010-0000-0000-000059000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 17"/>
+    <tableColumn id="90" xr3:uid="{00000000-0010-0000-0000-00005A000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 18"/>
+    <tableColumn id="91" xr3:uid="{00000000-0010-0000-0000-00005B000000}" name="Toelichting bij vraag 1 (optioneel) 18"/>
+    <tableColumn id="92" xr3:uid="{00000000-0010-0000-0000-00005C000000}" name="2. Mist er relevante juridische informatie? 18"/>
+    <tableColumn id="93" xr3:uid="{00000000-0010-0000-0000-00005D000000}" name="Toelichting bij vraag 2 (optioneel) 18"/>
+    <tableColumn id="94" xr3:uid="{00000000-0010-0000-0000-00005E000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 18"/>
+    <tableColumn id="95" xr3:uid="{00000000-0010-0000-0000-00005F000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 19"/>
+    <tableColumn id="96" xr3:uid="{00000000-0010-0000-0000-000060000000}" name="Toelichting bij vraag 1 (optioneel) 19"/>
+    <tableColumn id="97" xr3:uid="{00000000-0010-0000-0000-000061000000}" name="2. Mist er relevante juridische informatie? 19"/>
+    <tableColumn id="98" xr3:uid="{00000000-0010-0000-0000-000062000000}" name="Toelichting bij vraag 2 (optioneel) 19"/>
+    <tableColumn id="99" xr3:uid="{00000000-0010-0000-0000-000063000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 19"/>
+    <tableColumn id="100" xr3:uid="{00000000-0010-0000-0000-000064000000}" name="1. Klopt de uitleg juridisch? (0 = volledig onjuist, 5 = volledig correct) 20"/>
+    <tableColumn id="101" xr3:uid="{00000000-0010-0000-0000-000065000000}" name="Toelichting bij vraag 1 (optioneel) 20"/>
+    <tableColumn id="102" xr3:uid="{00000000-0010-0000-0000-000066000000}" name="2. Mist er relevante juridische informatie? 20"/>
+    <tableColumn id="103" xr3:uid="{00000000-0010-0000-0000-000067000000}" name="Toelichting bij vraag 2 (optioneel) 20"/>
+    <tableColumn id="104" xr3:uid="{00000000-0010-0000-0000-000068000000}" name="⚠️ Opgelet — verdient deze uitleg extra aandacht? 20"/>
   </tableColumns>
-  <tableStyleInfo name="Form responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Form responses 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -892,104 +883,107 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:CY4"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.88"/>
-    <col customWidth="1" min="2" max="2" width="23.13"/>
-    <col customWidth="1" min="3" max="3" width="22.88"/>
-    <col customWidth="1" min="4" max="5" width="37.63"/>
-    <col customWidth="1" min="6" max="6" width="29.38"/>
-    <col customWidth="1" min="7" max="7" width="35.13"/>
-    <col customWidth="1" min="8" max="8" width="29.38"/>
-    <col customWidth="1" min="9" max="10" width="37.63"/>
-    <col customWidth="1" min="11" max="11" width="29.38"/>
-    <col customWidth="1" min="12" max="12" width="35.13"/>
-    <col customWidth="1" min="13" max="13" width="29.38"/>
-    <col customWidth="1" min="14" max="15" width="37.63"/>
-    <col customWidth="1" min="16" max="16" width="29.38"/>
-    <col customWidth="1" min="17" max="17" width="35.13"/>
-    <col customWidth="1" min="18" max="18" width="29.38"/>
-    <col customWidth="1" min="19" max="20" width="37.63"/>
-    <col customWidth="1" min="21" max="21" width="29.38"/>
-    <col customWidth="1" min="22" max="22" width="35.13"/>
-    <col customWidth="1" min="23" max="23" width="29.38"/>
-    <col customWidth="1" min="24" max="25" width="37.63"/>
-    <col customWidth="1" min="26" max="26" width="29.38"/>
-    <col customWidth="1" min="27" max="27" width="35.13"/>
-    <col customWidth="1" min="28" max="28" width="29.38"/>
-    <col customWidth="1" min="29" max="30" width="37.63"/>
-    <col customWidth="1" min="31" max="31" width="29.38"/>
-    <col customWidth="1" min="32" max="32" width="35.13"/>
-    <col customWidth="1" min="33" max="33" width="29.38"/>
-    <col customWidth="1" min="34" max="35" width="37.63"/>
-    <col customWidth="1" min="36" max="36" width="29.38"/>
-    <col customWidth="1" min="37" max="37" width="35.13"/>
-    <col customWidth="1" min="38" max="38" width="29.38"/>
-    <col customWidth="1" min="39" max="40" width="37.63"/>
-    <col customWidth="1" min="41" max="41" width="29.38"/>
-    <col customWidth="1" min="42" max="42" width="35.13"/>
-    <col customWidth="1" min="43" max="43" width="29.38"/>
-    <col customWidth="1" min="44" max="45" width="37.63"/>
-    <col customWidth="1" min="46" max="46" width="29.38"/>
-    <col customWidth="1" min="47" max="47" width="35.13"/>
-    <col customWidth="1" min="48" max="48" width="29.38"/>
-    <col customWidth="1" min="49" max="50" width="37.63"/>
-    <col customWidth="1" min="51" max="51" width="29.38"/>
-    <col customWidth="1" min="52" max="52" width="35.13"/>
-    <col customWidth="1" min="53" max="53" width="29.38"/>
-    <col customWidth="1" min="54" max="55" width="37.63"/>
-    <col customWidth="1" min="56" max="56" width="29.38"/>
-    <col customWidth="1" min="57" max="57" width="35.13"/>
-    <col customWidth="1" min="58" max="58" width="29.38"/>
-    <col customWidth="1" min="59" max="60" width="37.63"/>
-    <col customWidth="1" min="61" max="61" width="29.38"/>
-    <col customWidth="1" min="62" max="62" width="35.13"/>
-    <col customWidth="1" min="63" max="63" width="29.38"/>
-    <col customWidth="1" min="64" max="65" width="37.63"/>
-    <col customWidth="1" min="66" max="66" width="29.38"/>
-    <col customWidth="1" min="67" max="67" width="35.13"/>
-    <col customWidth="1" min="68" max="68" width="29.38"/>
-    <col customWidth="1" min="69" max="70" width="37.63"/>
-    <col customWidth="1" min="71" max="71" width="29.38"/>
-    <col customWidth="1" min="72" max="72" width="35.13"/>
-    <col customWidth="1" min="73" max="73" width="29.38"/>
-    <col customWidth="1" min="74" max="75" width="37.63"/>
-    <col customWidth="1" min="76" max="76" width="29.38"/>
-    <col customWidth="1" min="77" max="77" width="35.13"/>
-    <col customWidth="1" min="78" max="78" width="29.38"/>
-    <col customWidth="1" min="79" max="80" width="37.63"/>
-    <col customWidth="1" min="81" max="81" width="29.38"/>
-    <col customWidth="1" min="82" max="82" width="35.13"/>
-    <col customWidth="1" min="83" max="83" width="29.38"/>
-    <col customWidth="1" min="84" max="85" width="37.63"/>
-    <col customWidth="1" min="86" max="86" width="29.38"/>
-    <col customWidth="1" min="87" max="87" width="35.13"/>
-    <col customWidth="1" min="88" max="88" width="29.38"/>
-    <col customWidth="1" min="89" max="90" width="37.63"/>
-    <col customWidth="1" min="91" max="91" width="29.38"/>
-    <col customWidth="1" min="92" max="92" width="35.13"/>
-    <col customWidth="1" min="93" max="93" width="29.38"/>
-    <col customWidth="1" min="94" max="95" width="37.63"/>
-    <col customWidth="1" min="96" max="96" width="29.38"/>
-    <col customWidth="1" min="97" max="97" width="35.13"/>
-    <col customWidth="1" min="98" max="98" width="29.38"/>
-    <col customWidth="1" min="99" max="100" width="37.63"/>
-    <col customWidth="1" min="101" max="101" width="29.38"/>
-    <col customWidth="1" min="102" max="102" width="35.13"/>
-    <col customWidth="1" min="103" max="103" width="29.38"/>
-    <col customWidth="1" min="104" max="104" width="37.63"/>
-    <col customWidth="1" min="105" max="110" width="18.88"/>
+    <col min="1" max="1" width="18.86328125" customWidth="1"/>
+    <col min="2" max="2" width="23.1328125" customWidth="1"/>
+    <col min="3" max="3" width="22.86328125" customWidth="1"/>
+    <col min="4" max="4" width="37.59765625" customWidth="1"/>
+    <col min="5" max="5" width="29.3984375" customWidth="1"/>
+    <col min="6" max="6" width="35.1328125" customWidth="1"/>
+    <col min="7" max="7" width="29.3984375" customWidth="1"/>
+    <col min="8" max="9" width="37.59765625" customWidth="1"/>
+    <col min="10" max="10" width="29.3984375" customWidth="1"/>
+    <col min="11" max="11" width="35.1328125" customWidth="1"/>
+    <col min="12" max="12" width="29.3984375" customWidth="1"/>
+    <col min="13" max="14" width="37.59765625" customWidth="1"/>
+    <col min="15" max="15" width="29.3984375" customWidth="1"/>
+    <col min="16" max="16" width="35.1328125" customWidth="1"/>
+    <col min="17" max="17" width="29.3984375" customWidth="1"/>
+    <col min="18" max="19" width="37.59765625" customWidth="1"/>
+    <col min="20" max="20" width="29.3984375" customWidth="1"/>
+    <col min="21" max="21" width="35.1328125" customWidth="1"/>
+    <col min="22" max="22" width="29.3984375" customWidth="1"/>
+    <col min="23" max="24" width="37.59765625" customWidth="1"/>
+    <col min="25" max="25" width="29.3984375" customWidth="1"/>
+    <col min="26" max="26" width="35.1328125" customWidth="1"/>
+    <col min="27" max="27" width="29.3984375" customWidth="1"/>
+    <col min="28" max="29" width="37.59765625" customWidth="1"/>
+    <col min="30" max="30" width="29.3984375" customWidth="1"/>
+    <col min="31" max="31" width="35.1328125" customWidth="1"/>
+    <col min="32" max="32" width="29.3984375" customWidth="1"/>
+    <col min="33" max="34" width="37.59765625" customWidth="1"/>
+    <col min="35" max="35" width="29.3984375" customWidth="1"/>
+    <col min="36" max="36" width="35.1328125" customWidth="1"/>
+    <col min="37" max="37" width="29.3984375" customWidth="1"/>
+    <col min="38" max="39" width="37.59765625" customWidth="1"/>
+    <col min="40" max="40" width="29.3984375" customWidth="1"/>
+    <col min="41" max="41" width="35.1328125" customWidth="1"/>
+    <col min="42" max="42" width="29.3984375" customWidth="1"/>
+    <col min="43" max="44" width="37.59765625" customWidth="1"/>
+    <col min="45" max="45" width="29.3984375" customWidth="1"/>
+    <col min="46" max="46" width="35.1328125" customWidth="1"/>
+    <col min="47" max="47" width="29.3984375" customWidth="1"/>
+    <col min="48" max="49" width="37.59765625" customWidth="1"/>
+    <col min="50" max="50" width="29.3984375" customWidth="1"/>
+    <col min="51" max="51" width="35.1328125" customWidth="1"/>
+    <col min="52" max="52" width="29.3984375" customWidth="1"/>
+    <col min="53" max="54" width="37.59765625" customWidth="1"/>
+    <col min="55" max="55" width="29.3984375" customWidth="1"/>
+    <col min="56" max="56" width="35.1328125" customWidth="1"/>
+    <col min="57" max="57" width="29.3984375" customWidth="1"/>
+    <col min="58" max="59" width="37.59765625" customWidth="1"/>
+    <col min="60" max="60" width="29.3984375" customWidth="1"/>
+    <col min="61" max="61" width="35.1328125" customWidth="1"/>
+    <col min="62" max="62" width="29.3984375" customWidth="1"/>
+    <col min="63" max="64" width="37.59765625" customWidth="1"/>
+    <col min="65" max="65" width="29.3984375" customWidth="1"/>
+    <col min="66" max="66" width="35.1328125" customWidth="1"/>
+    <col min="67" max="67" width="29.3984375" customWidth="1"/>
+    <col min="68" max="69" width="37.59765625" customWidth="1"/>
+    <col min="70" max="70" width="29.3984375" customWidth="1"/>
+    <col min="71" max="71" width="35.1328125" customWidth="1"/>
+    <col min="72" max="72" width="29.3984375" customWidth="1"/>
+    <col min="73" max="74" width="37.59765625" customWidth="1"/>
+    <col min="75" max="75" width="29.3984375" customWidth="1"/>
+    <col min="76" max="76" width="35.1328125" customWidth="1"/>
+    <col min="77" max="77" width="29.3984375" customWidth="1"/>
+    <col min="78" max="79" width="37.59765625" customWidth="1"/>
+    <col min="80" max="80" width="29.3984375" customWidth="1"/>
+    <col min="81" max="81" width="35.1328125" customWidth="1"/>
+    <col min="82" max="82" width="29.3984375" customWidth="1"/>
+    <col min="83" max="84" width="37.59765625" customWidth="1"/>
+    <col min="85" max="85" width="29.3984375" customWidth="1"/>
+    <col min="86" max="86" width="35.1328125" customWidth="1"/>
+    <col min="87" max="87" width="29.3984375" customWidth="1"/>
+    <col min="88" max="89" width="37.59765625" customWidth="1"/>
+    <col min="90" max="90" width="29.3984375" customWidth="1"/>
+    <col min="91" max="91" width="35.1328125" customWidth="1"/>
+    <col min="92" max="92" width="29.3984375" customWidth="1"/>
+    <col min="93" max="94" width="37.59765625" customWidth="1"/>
+    <col min="95" max="95" width="29.3984375" customWidth="1"/>
+    <col min="96" max="96" width="35.1328125" customWidth="1"/>
+    <col min="97" max="97" width="29.3984375" customWidth="1"/>
+    <col min="98" max="99" width="37.59765625" customWidth="1"/>
+    <col min="100" max="100" width="29.3984375" customWidth="1"/>
+    <col min="101" max="101" width="35.1328125" customWidth="1"/>
+    <col min="102" max="102" width="29.3984375" customWidth="1"/>
+    <col min="103" max="103" width="37.59765625" customWidth="1"/>
+    <col min="104" max="109" width="18.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" spans="1:103" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1299,481 +1293,703 @@
       <c r="CY1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:103" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>46157.742000497688</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>103</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="3">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" s="3">
+        <v>4</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="M2" s="4"/>
+      <c r="N2" s="3">
+        <v>4</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="S2" s="3">
+        <v>4</v>
+      </c>
+      <c r="T2" s="4"/>
+      <c r="U2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="V2" s="4"/>
+      <c r="W2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="X2" s="3">
+        <v>4</v>
+      </c>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK2" s="4"/>
+      <c r="AL2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AM2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AN2" s="4"/>
+      <c r="AO2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AP2" s="4"/>
+      <c r="AQ2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AS2" s="4"/>
+      <c r="AT2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AU2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AV2" s="4"/>
+      <c r="AW2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AX2" s="4"/>
+      <c r="AY2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AZ2" s="4"/>
+      <c r="BA2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="BB2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BC2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BE2" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BF2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="BG2" s="3">
+        <v>4</v>
+      </c>
+      <c r="BH2" s="4"/>
+      <c r="BI2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="BJ2" s="4"/>
+      <c r="BK2" s="4"/>
+      <c r="BL2" s="3">
+        <v>1</v>
+      </c>
+      <c r="BM2" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BO2" s="4"/>
+      <c r="BP2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="BQ2" s="3">
+        <v>4</v>
+      </c>
+      <c r="BR2" s="4"/>
+      <c r="BS2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="BT2" s="4"/>
+      <c r="BU2" s="4"/>
+      <c r="BV2" s="3">
+        <v>1</v>
+      </c>
+      <c r="BW2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BX2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BY2" s="4"/>
+      <c r="BZ2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="CA2" s="3">
+        <v>4</v>
+      </c>
+      <c r="CB2" s="4"/>
+      <c r="CC2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="CD2" s="4"/>
+      <c r="CE2" s="4"/>
+      <c r="CF2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CG2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CH2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="CI2" s="4"/>
+      <c r="CJ2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="CK2" s="3">
+        <v>4</v>
+      </c>
+      <c r="CL2" s="4"/>
+      <c r="CM2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="CN2" s="4"/>
+      <c r="CO2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="CP2" s="3">
+        <v>4</v>
+      </c>
+      <c r="CQ2" s="4"/>
+      <c r="CR2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="CS2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CT2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="CU2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CV2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CW2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="CX2" s="4"/>
+      <c r="CY2" s="3" t="s">
+        <v>108</v>
+      </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="2">
-        <v>46157.74200049769</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="3" spans="1:103" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5">
+        <v>46158.544039351851</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="D3" s="6">
+        <v>4</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="H3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I3" s="6">
+        <v>3</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6">
+        <v>4</v>
+      </c>
+      <c r="O3" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="T2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="U2" s="4"/>
-      <c r="V2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="W2" s="4"/>
-      <c r="X2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="3" t="s">
+      <c r="P3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="S3" s="6">
+        <v>4</v>
+      </c>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6">
+        <v>4</v>
+      </c>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="6"/>
+      <c r="AH3" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI3" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG2" s="4"/>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="AJ2" s="3" t="s">
+      <c r="AJ3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK3" s="6"/>
+      <c r="AL3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AM3" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN3" s="6"/>
+      <c r="AO3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AP3" s="6"/>
+      <c r="AQ3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR3" s="6">
+        <v>4</v>
+      </c>
+      <c r="AS3" s="6"/>
+      <c r="AT3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AU3" s="6"/>
+      <c r="AV3" s="6"/>
+      <c r="AW3" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="AK2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AL2" s="4"/>
-      <c r="AM2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AN2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="AO2" s="4"/>
-      <c r="AP2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ2" s="4"/>
-      <c r="AR2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AS2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="AT2" s="4"/>
-      <c r="AU2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV2" s="3" t="s">
+      <c r="AX3" s="6"/>
+      <c r="AY3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AZ3" s="6"/>
+      <c r="BA3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="BB3" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="AW2" s="4"/>
-      <c r="AX2" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AY2" s="4"/>
-      <c r="AZ2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="BA2" s="4"/>
-      <c r="BB2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="BC2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BD2" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BE2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="BF2" s="3" t="s">
+      <c r="BC3" s="6"/>
+      <c r="BD3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="BE3" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="BF3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="BG3" s="6">
+        <v>4</v>
+      </c>
+      <c r="BH3" s="6"/>
+      <c r="BI3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="BJ3" s="6"/>
+      <c r="BK3" s="6"/>
+      <c r="BL3" s="6">
+        <v>3</v>
+      </c>
+      <c r="BM3" s="6"/>
+      <c r="BN3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="BO3" s="6"/>
+      <c r="BP3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="BQ3" s="6">
+        <v>4</v>
+      </c>
+      <c r="BR3" s="6"/>
+      <c r="BS3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="BT3" s="6"/>
+      <c r="BU3" s="6"/>
+      <c r="BV3" s="6">
+        <v>1</v>
+      </c>
+      <c r="BW3" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="BG2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="BI2" s="4"/>
-      <c r="BJ2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="BK2" s="4"/>
-      <c r="BL2" s="4"/>
-      <c r="BM2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="BN2" s="3" t="s">
+      <c r="BX3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="BY3" s="6"/>
+      <c r="BZ3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="CA3" s="6">
+        <v>4</v>
+      </c>
+      <c r="CB3" s="6"/>
+      <c r="CC3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="CD3" s="6"/>
+      <c r="CE3" s="6"/>
+      <c r="CF3" s="6">
+        <v>1</v>
+      </c>
+      <c r="CG3" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="BO2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="BP2" s="4"/>
-      <c r="BQ2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="BR2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="BS2" s="4"/>
-      <c r="BT2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="BU2" s="4"/>
-      <c r="BV2" s="4"/>
-      <c r="BW2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="BX2" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BY2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="BZ2" s="4"/>
-      <c r="CA2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="CB2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="CC2" s="4"/>
-      <c r="CD2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="CE2" s="4"/>
-      <c r="CF2" s="4"/>
-      <c r="CG2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="CH2" s="3" t="s">
+      <c r="CH3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="CI3" s="6"/>
+      <c r="CJ3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="CK3" s="6">
+        <v>4</v>
+      </c>
+      <c r="CL3" s="6"/>
+      <c r="CM3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="CN3" s="6"/>
+      <c r="CO3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="CP3" s="6">
+        <v>4</v>
+      </c>
+      <c r="CQ3" s="6"/>
+      <c r="CR3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="CS3" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="CT3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="CU3" s="6">
+        <v>2</v>
+      </c>
+      <c r="CV3" s="6"/>
+      <c r="CW3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="CX3" s="6"/>
+      <c r="CY3" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:103" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
+        <v>46159.707882766204</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="CI2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="CJ2" s="4"/>
-      <c r="CK2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="CL2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="CM2" s="4"/>
-      <c r="CN2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="CO2" s="4"/>
-      <c r="CP2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="CQ2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="CR2" s="4"/>
-      <c r="CS2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="CT2" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CU2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="CV2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="CW2" s="3" t="s">
+      <c r="D4" s="6">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="CX2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="CY2" s="4"/>
-      <c r="CZ2" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="5">
-        <v>46159.707882766204</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="F4" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I4" s="6">
+        <v>3</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="K4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="N4" s="6">
+        <v>3</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q4" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="R4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="S4" s="6">
+        <v>4</v>
+      </c>
+      <c r="T4" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="U4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="V4" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="J3" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="K3" s="6" t="s">
+      <c r="W4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AC4" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE4" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="L3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="O3" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="R3" s="6" t="s">
+      <c r="AH4" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI4" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="S3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="T3" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="U3" s="6" t="s">
+      <c r="AJ4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AL4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AM4" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN4" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="V3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="W3" s="6" t="s">
+      <c r="AO4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR4" s="6">
+        <v>4</v>
+      </c>
+      <c r="AS4" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="X3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AD3" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="AF3" s="6" t="s">
+      <c r="AT4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AV4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AW4" s="6">
+        <v>4</v>
+      </c>
+      <c r="AY4" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="BB4" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="BC4" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="AI3" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="AJ3" s="6" t="s">
+      <c r="BD4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="BF4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="BG4" s="6">
+        <v>4</v>
+      </c>
+      <c r="BH4" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="AK3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="AN3" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="AO3" s="6" t="s">
+      <c r="BI4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ4" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="AP3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="AS3" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="AT3" s="6" t="s">
+      <c r="BL4" s="6">
+        <v>4</v>
+      </c>
+      <c r="BN4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="BO4" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AU3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="AW3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="AX3" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="AZ3" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="BC3" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="BD3" s="6" t="s">
+      <c r="BP4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="BQ4" s="6">
+        <v>2</v>
+      </c>
+      <c r="BR4" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="BE3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="BG3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH3" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="BI3" s="6" t="s">
+      <c r="BS4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="BU4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="BV4" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="BX4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="CA4" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="CC4" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="CF4" s="6">
+        <v>4</v>
+      </c>
+      <c r="CH4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="CI4" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="BJ3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="BK3" s="6" t="s">
+      <c r="CK4" s="6">
+        <v>4</v>
+      </c>
+      <c r="CL4" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="BM3" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="BO3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="BP3" s="6" t="s">
+      <c r="CM4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="CO4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="CP4" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="CQ4" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="BQ3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="BR3" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="BS3" s="6" t="s">
+      <c r="CR4" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="CU4" s="6">
+        <v>4</v>
+      </c>
+      <c r="CW4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="CX4" s="6" t="s">
         <v>142</v>
-      </c>
-      <c r="BT3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="BV3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="BW3" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="BY3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="CB3" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="CD3" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="CG3" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="CI3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="CJ3" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="CL3" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="CM3" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="CN3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="CP3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="CQ3" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="CR3" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="CS3" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="CV3" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="CX3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="CY3" s="6" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>